--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00950B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00950B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1EA3692-9AA9-4E29-A3D2-DAAEF7F47BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2889F94-33EE-4DAF-A989-406313D9BC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{5DF9A1E5-066B-4B1F-98A2-0DC652FA12AE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{BD7C1AE2-FD1B-44B7-9FDE-6D45CA86279A}"/>
   </bookViews>
   <sheets>
     <sheet name="00950B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1558,24 +1558,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E581C0F2-1FDA-4BC8-BDAD-DBFFC8CBA7F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F1F350-277D-4BBC-B2FC-C9CF72E5C25A}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1603,7 +1604,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1633,7 +1634,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1679,7 +1680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1729,7 +1730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1783,7 +1784,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1809,7 +1810,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1865,7 +1866,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1921,7 +1922,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2032,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2087,7 +2088,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2255,7 +2256,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2367,7 +2368,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2423,7 +2424,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2479,7 +2480,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2591,7 +2592,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2647,7 +2648,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2701,7 +2702,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2813,7 +2814,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
         <v>57</v>
       </c>
